--- a/imageCreationExcel/Bright/Master/MASTER_6.xlsx
+++ b/imageCreationExcel/Bright/Master/MASTER_6.xlsx
@@ -552,15 +552,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\3_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K2" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>M_6_1_5_unmatch_3_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_1_5_unmatch_3_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -606,15 +612,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\5_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K3" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>M_6_2_J_filler_5_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_2_J_filler_5_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -714,15 +726,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\8_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K5" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
       <c r="N5" t="inlineStr"/>
       <c r="O5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>M_6_4_L_filler_8_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_4_L_filler_8_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -768,15 +786,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr"/>
-      <c r="M6" t="inlineStr"/>
-      <c r="N6" t="inlineStr"/>
-      <c r="O6" t="inlineStr"/>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K6" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M6" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O6" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>M_6_5_1_match_1_day_sun_empty_MODEL.jpg</t>
+          <t>M_6_5_1_match_1_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -876,15 +912,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K8" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L8" t="inlineStr"/>
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>M_6_7_4_match_4_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_7_4_match_4_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -930,15 +972,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\0_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr"/>
-      <c r="M9" t="inlineStr"/>
-      <c r="N9" t="inlineStr"/>
-      <c r="O9" t="inlineStr"/>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K9" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M9" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O9" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>M_6_8_A_filler_0_day_rain_busy_MODEL.jpg</t>
+          <t>M_6_8_A_filler_0_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -984,15 +1044,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K10" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L10" t="inlineStr"/>
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>M_6_9_I_filler_1_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_9_I_filler_1_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1038,15 +1104,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\2_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K11" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>M_6_10_T_filler_2_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_10_T_filler_2_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1146,15 +1218,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\4_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K13" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L13" t="inlineStr"/>
       <c r="M13" t="inlineStr"/>
       <c r="N13" t="inlineStr"/>
       <c r="O13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>M_6_12_G_filler_4_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_12_G_filler_4_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1200,15 +1278,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\1_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr"/>
-      <c r="M14" t="inlineStr"/>
-      <c r="N14" t="inlineStr"/>
-      <c r="O14" t="inlineStr"/>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K14" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O14" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
-          <t>M_6_13_R_filler_1_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_13_R_filler_1_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1254,15 +1350,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\5_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr"/>
-      <c r="M15" t="inlineStr"/>
-      <c r="N15" t="inlineStr"/>
-      <c r="O15" t="inlineStr"/>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K15" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M15" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O15" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>M_6_14_5_match_5_day_sun_empty_MODEL.jpg</t>
+          <t>M_6_14_5_match_5_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -1362,15 +1476,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\0_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K17" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
       <c r="P17" t="inlineStr">
         <is>
-          <t>M_6_16_G_filler_0_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_16_G_filler_0_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1524,15 +1644,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\7_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr"/>
-      <c r="M20" t="inlineStr"/>
-      <c r="N20" t="inlineStr"/>
-      <c r="O20" t="inlineStr"/>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K20" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M20" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O20" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>M_6_19_4_unmatch_7_day_rain_busy_MODEL.jpg</t>
+          <t>M_6_19_4_unmatch_7_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1578,15 +1716,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K21" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L21" t="inlineStr"/>
       <c r="M21" t="inlineStr"/>
       <c r="N21" t="inlineStr"/>
       <c r="O21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>M_6_20_P_filler_2_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_20_P_filler_2_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -1686,15 +1830,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\0_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr"/>
-      <c r="M23" t="inlineStr"/>
-      <c r="N23" t="inlineStr"/>
-      <c r="O23" t="inlineStr"/>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K23" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M23" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O23" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>M_6_22_0_match_0_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_22_0_match_0_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -1740,15 +1902,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\2_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr"/>
-      <c r="M24" t="inlineStr"/>
-      <c r="N24" t="inlineStr"/>
-      <c r="O24" t="inlineStr"/>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K24" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M24" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N24" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O24" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P24" t="inlineStr">
         <is>
-          <t>M_6_23_A_filler_2_day_rain_busy_MODEL.jpg</t>
+          <t>M_6_23_A_filler_2_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -1794,15 +1974,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\7_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K25" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L25" t="inlineStr"/>
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>M_6_24_G_filler_7_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_24_G_filler_7_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -1848,15 +2034,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\1_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K26" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>M_6_25_R_filler_1_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_25_R_filler_1_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -1956,15 +2148,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\7_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr"/>
-      <c r="M28" t="inlineStr"/>
-      <c r="N28" t="inlineStr"/>
-      <c r="O28" t="inlineStr"/>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K28" t="n">
+        <v>23.168</v>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M28" t="n">
+        <v>1.169</v>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O28" t="n">
+        <v>1.078</v>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
-          <t>M_6_27_C_filler_7_day_rain_busy_MODEL.jpg</t>
+          <t>M_6_27_C_filler_7_day_rain_busy_MODEL_brightness23.168_contrast1.169_gamma1.078.jpg</t>
         </is>
       </c>
     </row>
@@ -2010,15 +2220,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr"/>
-      <c r="M29" t="inlineStr"/>
-      <c r="N29" t="inlineStr"/>
-      <c r="O29" t="inlineStr"/>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K29" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M29" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O29" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>M_6_28_G_filler_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_28_G_filler_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2118,15 +2346,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\7_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K31" t="n">
+        <v>40.55</v>
+      </c>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>M_6_30_L_filler_7_day_sun_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_30_L_filler_7_day_sun_empty_BRIGHTONLY_brightness40.550.jpg</t>
         </is>
       </c>
     </row>
@@ -2172,15 +2406,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\7_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr"/>
-      <c r="M32" t="inlineStr"/>
-      <c r="N32" t="inlineStr"/>
-      <c r="O32" t="inlineStr"/>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K32" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M32" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N32" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O32" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>M_6_31_8_unmatch_7_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_31_8_unmatch_7_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2334,15 +2586,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\5_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr"/>
-      <c r="M35" t="inlineStr"/>
-      <c r="N35" t="inlineStr"/>
-      <c r="O35" t="inlineStr"/>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K35" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M35" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
-          <t>M_6_34_P_filler_5_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_34_P_filler_5_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2442,15 +2712,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\2_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr"/>
-      <c r="M37" t="inlineStr"/>
-      <c r="N37" t="inlineStr"/>
-      <c r="O37" t="inlineStr"/>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K37" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M37" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
-          <t>M_6_36_C_filler_2_day_sun_busy_MODEL.jpg</t>
+          <t>M_6_36_C_filler_2_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2550,15 +2838,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_busy\3_day_rain_busy.jpg</t>
         </is>
       </c>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K39" t="n">
+        <v>36.09</v>
+      </c>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>M_6_38_R_filler_3_day_rain_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_38_R_filler_3_day_rain_busy_BRIGHTONLY_brightness36.090.jpg</t>
         </is>
       </c>
     </row>
@@ -2604,15 +2898,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\9_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K40" t="n">
+        <v>35.62</v>
+      </c>
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr"/>
       <c r="N40" t="inlineStr"/>
       <c r="O40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>M_6_39_8_unmatch_9_day_rain_empty_BRIGHTONLY.jpg</t>
+          <t>M_6_39_8_unmatch_9_day_rain_empty_BRIGHTONLY_brightness35.620.jpg</t>
         </is>
       </c>
     </row>
@@ -2658,15 +2958,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_empty\3_day_sun_empty.jpg</t>
         </is>
       </c>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr"/>
-      <c r="M41" t="inlineStr"/>
-      <c r="N41" t="inlineStr"/>
-      <c r="O41" t="inlineStr"/>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K41" t="n">
+        <v>18.052</v>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M41" t="n">
+        <v>1.163</v>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>1.019</v>
+      </c>
       <c r="P41" t="inlineStr">
         <is>
-          <t>M_6_40_J_filler_3_day_sun_empty_MODEL.jpg</t>
+          <t>M_6_40_J_filler_3_day_sun_empty_MODEL_brightness18.052_contrast1.163_gamma1.019.jpg</t>
         </is>
       </c>
     </row>
@@ -2766,15 +3084,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\2_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr"/>
-      <c r="N43" t="inlineStr"/>
-      <c r="O43" t="inlineStr"/>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K43" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M43" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P43" t="inlineStr">
         <is>
-          <t>M_6_42_2_match_2_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_42_2_match_2_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2874,15 +3210,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\rain_empty\4_day_rain_empty.jpg</t>
         </is>
       </c>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr"/>
-      <c r="M45" t="inlineStr"/>
-      <c r="N45" t="inlineStr"/>
-      <c r="O45" t="inlineStr"/>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K45" t="n">
+        <v>22.602</v>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M45" t="n">
+        <v>1.158</v>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>1.045</v>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>M_6_44_A_filler_4_day_rain_empty_MODEL.jpg</t>
+          <t>M_6_44_A_filler_4_day_rain_empty_MODEL_brightness22.602_contrast1.158_gamma1.045.jpg</t>
         </is>
       </c>
     </row>
@@ -2928,15 +3282,33 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr"/>
-      <c r="N46" t="inlineStr"/>
-      <c r="O46" t="inlineStr"/>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K46" t="n">
+        <v>25.454</v>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>contrast</t>
+        </is>
+      </c>
+      <c r="M46" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>gamma</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>1.064</v>
+      </c>
       <c r="P46" t="inlineStr">
         <is>
-          <t>M_6_45_F_filler_3_day_sun_busy_MODEL.jpg</t>
+          <t>M_6_45_F_filler_3_day_sun_busy_MODEL_brightness25.454_contrast1.160_gamma1.064.jpg</t>
         </is>
       </c>
     </row>
@@ -2982,15 +3354,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\5_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K47" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>M_6_46_7_unmatch_5_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_46_7_unmatch_5_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
@@ -3090,15 +3468,21 @@
           <t>G:\pictures_verify\transformed_verify\roomBright_figureDark\sun_busy\3_day_sun_busy.jpg</t>
         </is>
       </c>
-      <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr"/>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>brightness</t>
+        </is>
+      </c>
+      <c r="K49" t="n">
+        <v>45.47</v>
+      </c>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>M_6_48_3_match_3_day_sun_busy_BRIGHTONLY.jpg</t>
+          <t>M_6_48_3_match_3_day_sun_busy_BRIGHTONLY_brightness45.470.jpg</t>
         </is>
       </c>
     </row>
